--- a/mini-projet-trey-pp/annexes/cases/power_profile_case_5_sum_week.xlsx
+++ b/mini-projet-trey-pp/annexes/cases/power_profile_case_5_sum_week.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\sebpfister\rhtlab\mini-projet-trey-pp\annexes\cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{633D05A3-3EA9-4712-9723-8F29C185EF3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB423DB2-752A-4945-8FE8-41B214F5448D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="735" windowWidth="22485" windowHeight="14265" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="165" yWindow="210" windowWidth="22485" windowHeight="14265" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="load" sheetId="1" r:id="rId1"/>
